--- a/QAFoxDemo/src/test/resources/TestDataFile.xlsx
+++ b/QAFoxDemo/src/test/resources/TestDataFile.xlsx
@@ -3,20 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mylambigai\Selenium_basic\QAFoxDemo\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB31294-5887-4ACE-B306-599EBCE17669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E408BD51-A442-418F-A590-8825A7816FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:Q11"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>password</t>
   </si>
@@ -44,6 +41,9 @@
   </si>
   <si>
     <t>mac</t>
+  </si>
+  <si>
+    <t>juug</t>
   </si>
 </sst>
 </file>
@@ -441,4 +441,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECC56BA-B1DD-4A75-9C8F-94861D82728C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>